--- a/Asegurados_SIS/Data/Asegurados_Por_Punto_de_Digitacion.xlsx
+++ b/Asegurados_SIS/Data/Asegurados_Por_Punto_de_Digitacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos_python\DashboardExcel\Asegurados_SIS\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A65DDFCE-0513-4E18-A5ED-0EE451D6D663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C371C6BE-E931-4DD6-AEFC-B64CE0117797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{040CB8E9-F33A-44EA-9A69-6A6860FC6EB8}"/>
+    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{9D753A2A-9E33-42FD-B822-73085AED7299}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -958,7 +958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F166CD5A-85EF-4131-8D97-013C60B6079D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA787564-6685-4047-B740-010E07B3A3AA}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>17864</v>
+        <v>17914</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17038</v>
+        <v>17095</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1009,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>13661</v>
+        <v>13511</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>9359</v>
+        <v>9321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1031,7 +1031,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>8405</v>
+        <v>8319</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>7829</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1053,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>7805</v>
+        <v>7781</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1064,7 +1064,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>6452</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1075,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>6166</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1086,7 +1086,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1">
-        <v>5286</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="1">
-        <v>4782</v>
+        <v>4772</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1108,7 +1108,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="1">
-        <v>4633</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="1">
-        <v>3368</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1130,7 +1130,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>3070</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1141,7 +1141,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="1">
-        <v>3062</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1152,7 +1152,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="1">
-        <v>3044</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1163,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="1">
-        <v>2899</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1174,7 +1174,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="1">
-        <v>2815</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1185,7 +1185,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="1">
-        <v>2793</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1196,7 +1196,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="1">
-        <v>2396</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1207,7 +1207,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="1">
-        <v>1995</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1218,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="1">
-        <v>1304</v>
+        <v>1293</v>
       </c>
     </row>
   </sheetData>
